--- a/reports/model_comparison_report.xlsx
+++ b/reports/model_comparison_report.xlsx
@@ -507,13 +507,13 @@
         <v>0.5355</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4814</v>
+        <v>1.5594</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8069</v>
+        <v>2.8024</v>
       </c>
       <c r="K2" t="n">
-        <v>0.025379</v>
+        <v>0.018683</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -529,31 +529,31 @@
         <v>150</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0501</v>
+        <v>0.0512</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0621</v>
+        <v>0.0659</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8981</v>
+        <v>0.8933</v>
       </c>
       <c r="G3" t="n">
         <v>0.6961000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6999</v>
+        <v>0.6994</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0898</v>
+        <v>0.0741</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7041</v>
+        <v>2.8496</v>
       </c>
       <c r="K3" t="n">
-        <v>0.024694</v>
+        <v>0.018997</v>
       </c>
       <c r="L3" t="n">
         <v>87.58</v>
@@ -587,13 +587,13 @@
         <v>0.5355</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3424</v>
+        <v>0.3172</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6673</v>
+        <v>3.7033</v>
       </c>
       <c r="K4" t="n">
-        <v>0.031116</v>
+        <v>0.024689</v>
       </c>
       <c r="L4" t="n">
         <v>5.74</v>
@@ -6070,10 +6070,10 @@
         <v>0.85</v>
       </c>
       <c r="D152" t="n">
-        <v>0.8913631439208984</v>
+        <v>0.8837324380874634</v>
       </c>
       <c r="E152" t="n">
-        <v>0.04136314392089846</v>
+        <v>0.0337324380874634</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -6106,10 +6106,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D153" t="n">
-        <v>0.8766825199127197</v>
+        <v>0.8682591319084167</v>
       </c>
       <c r="E153" t="n">
-        <v>0.06331748008728022</v>
+        <v>0.0717408680915832</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
         <v>0.22</v>
       </c>
       <c r="D154" t="n">
-        <v>0.3334362208843231</v>
+        <v>0.3238843083381653</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1134362208843231</v>
+        <v>0.1038843083381653</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         <v>0.36</v>
       </c>
       <c r="D155" t="n">
-        <v>0.3406344056129456</v>
+        <v>0.334473580121994</v>
       </c>
       <c r="E155" t="n">
-        <v>0.01936559438705443</v>
+        <v>0.02552641987800597</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -6214,10 +6214,10 @@
         <v>0.74</v>
       </c>
       <c r="D156" t="n">
-        <v>0.651868462562561</v>
+        <v>0.6762700080871582</v>
       </c>
       <c r="E156" t="n">
-        <v>0.08813153743743896</v>
+        <v>0.06372999191284179</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -6250,10 +6250,10 @@
         <v>0.9</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9261105060577393</v>
+        <v>0.9217685461044312</v>
       </c>
       <c r="E157" t="n">
-        <v>0.02611050605773924</v>
+        <v>0.02176854610443113</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -6286,10 +6286,10 @@
         <v>0.64</v>
       </c>
       <c r="D158" t="n">
-        <v>0.67581707239151</v>
+        <v>0.710309624671936</v>
       </c>
       <c r="E158" t="n">
-        <v>0.03581707239151</v>
+        <v>0.07030962467193602</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
         <v>0.77</v>
       </c>
       <c r="D159" t="n">
-        <v>0.6494914889335632</v>
+        <v>0.6899715065956116</v>
       </c>
       <c r="E159" t="n">
-        <v>0.1205085110664368</v>
+        <v>0.08002849340438845</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -6358,10 +6358,10 @@
         <v>0.31</v>
       </c>
       <c r="D160" t="n">
-        <v>0.3474389314651489</v>
+        <v>0.3342460095882416</v>
       </c>
       <c r="E160" t="n">
-        <v>0.03743893146514893</v>
+        <v>0.02424600958824158</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -6394,10 +6394,10 @@
         <v>0.73</v>
       </c>
       <c r="D161" t="n">
-        <v>0.7780437469482422</v>
+        <v>0.7805025577545166</v>
       </c>
       <c r="E161" t="n">
-        <v>0.04804374694824221</v>
+        <v>0.05050255775451662</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -6430,10 +6430,10 @@
         <v>0.61</v>
       </c>
       <c r="D162" t="n">
-        <v>0.6373809576034546</v>
+        <v>0.6532515287399292</v>
       </c>
       <c r="E162" t="n">
-        <v>0.0273809576034546</v>
+        <v>0.04325152873992921</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -6466,10 +6466,10 @@
         <v>0.91</v>
       </c>
       <c r="D163" t="n">
-        <v>0.8539953231811523</v>
+        <v>0.8506841659545898</v>
       </c>
       <c r="E163" t="n">
-        <v>0.05600467681884769</v>
+        <v>0.05931583404541019</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -6502,10 +6502,10 @@
         <v>0.78</v>
       </c>
       <c r="D164" t="n">
-        <v>0.7615817785263062</v>
+        <v>0.7372086644172668</v>
       </c>
       <c r="E164" t="n">
-        <v>0.01841822147369387</v>
+        <v>0.04279133558273318</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D165" t="n">
-        <v>0.8564279675483704</v>
+        <v>0.8512243628501892</v>
       </c>
       <c r="E165" t="n">
-        <v>0.08357203245162959</v>
+        <v>0.08877563714981074</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -6574,10 +6574,10 @@
         <v>0.86</v>
       </c>
       <c r="D166" t="n">
-        <v>0.7830823659896851</v>
+        <v>0.7750399112701416</v>
       </c>
       <c r="E166" t="n">
-        <v>0.07691763401031493</v>
+        <v>0.08496008872985839</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -6610,10 +6610,10 @@
         <v>0.95</v>
       </c>
       <c r="D167" t="n">
-        <v>0.9265522360801697</v>
+        <v>0.9040381908416748</v>
       </c>
       <c r="E167" t="n">
-        <v>0.02344776391983028</v>
+        <v>0.04596180915832515</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -6646,10 +6646,10 @@
         <v>0.16</v>
       </c>
       <c r="D168" t="n">
-        <v>0.238301619887352</v>
+        <v>0.2258034646511078</v>
       </c>
       <c r="E168" t="n">
-        <v>0.07830161988735199</v>
+        <v>0.06580346465110778</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -6682,10 +6682,10 @@
         <v>0.91</v>
       </c>
       <c r="D169" t="n">
-        <v>0.8183086514472961</v>
+        <v>0.8117124438285828</v>
       </c>
       <c r="E169" t="n">
-        <v>0.09169134855270389</v>
+        <v>0.09828755617141727</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -6718,10 +6718,10 @@
         <v>0.89</v>
       </c>
       <c r="D170" t="n">
-        <v>0.8451523780822754</v>
+        <v>0.8442110419273376</v>
       </c>
       <c r="E170" t="n">
-        <v>0.04484762191772462</v>
+        <v>0.04578895807266237</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -6754,10 +6754,10 @@
         <v>0.33</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3003141582012177</v>
+        <v>0.2911826968193054</v>
       </c>
       <c r="E171" t="n">
-        <v>0.02968584179878236</v>
+        <v>0.0388173031806946</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
         <v>0.9</v>
       </c>
       <c r="D172" t="n">
-        <v>0.9048417806625366</v>
+        <v>0.9063891172409058</v>
       </c>
       <c r="E172" t="n">
-        <v>0.004841780662536599</v>
+        <v>0.00638911724090574</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -6826,10 +6826,10 @@
         <v>0.62</v>
       </c>
       <c r="D173" t="n">
-        <v>0.7001932263374329</v>
+        <v>0.7392617464065552</v>
       </c>
       <c r="E173" t="n">
-        <v>0.08019322633743287</v>
+        <v>0.1192617464065552</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -6862,10 +6862,10 @@
         <v>0.41</v>
       </c>
       <c r="D174" t="n">
-        <v>0.3380424678325653</v>
+        <v>0.326810359954834</v>
       </c>
       <c r="E174" t="n">
-        <v>0.07195753216743467</v>
+        <v>0.08318964004516599</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -6898,10 +6898,10 @@
         <v>0.82</v>
       </c>
       <c r="D175" t="n">
-        <v>0.9059644341468811</v>
+        <v>0.8977856040000916</v>
       </c>
       <c r="E175" t="n">
-        <v>0.08596443414688115</v>
+        <v>0.0777856040000916</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -6934,10 +6934,10 @@
         <v>0.84</v>
       </c>
       <c r="D176" t="n">
-        <v>0.9134972095489502</v>
+        <v>0.9108246564865112</v>
       </c>
       <c r="E176" t="n">
-        <v>0.07349720954895023</v>
+        <v>0.07082465648651126</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -6970,10 +6970,10 @@
         <v>0.88</v>
       </c>
       <c r="D177" t="n">
-        <v>0.8989501595497131</v>
+        <v>0.8963189125061035</v>
       </c>
       <c r="E177" t="n">
-        <v>0.01895015954971313</v>
+        <v>0.01631891250610351</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         <v>0.77</v>
       </c>
       <c r="D178" t="n">
-        <v>0.7263143062591553</v>
+        <v>0.7667015194892883</v>
       </c>
       <c r="E178" t="n">
-        <v>0.04368569374084474</v>
+        <v>0.003298480510711688</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -7042,10 +7042,10 @@
         <v>0.67</v>
       </c>
       <c r="D179" t="n">
-        <v>0.6587129831314087</v>
+        <v>0.671537458896637</v>
       </c>
       <c r="E179" t="n">
-        <v>0.01128701686859135</v>
+        <v>0.001537458896636923</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -7078,10 +7078,10 @@
         <v>0.75</v>
       </c>
       <c r="D180" t="n">
-        <v>0.6616864800453186</v>
+        <v>0.6773990392684937</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0883135199546814</v>
+        <v>0.07260096073150635</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -7114,10 +7114,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="D181" t="n">
-        <v>0.6202354431152344</v>
+        <v>0.5989513397216797</v>
       </c>
       <c r="E181" t="n">
-        <v>0.06023544311523432</v>
+        <v>0.03895133972167963</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -7150,10 +7150,10 @@
         <v>0.39</v>
       </c>
       <c r="D182" t="n">
-        <v>0.3242031931877136</v>
+        <v>0.3009508848190308</v>
       </c>
       <c r="E182" t="n">
-        <v>0.06579680681228639</v>
+        <v>0.08904911518096925</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         <v>0.36</v>
       </c>
       <c r="D183" t="n">
-        <v>0.2493091225624084</v>
+        <v>0.1816143393516541</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1106908774375915</v>
+        <v>0.1783856606483459</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -7222,10 +7222,10 @@
         <v>0.9</v>
       </c>
       <c r="D184" t="n">
-        <v>0.8960310220718384</v>
+        <v>0.8934342265129089</v>
       </c>
       <c r="E184" t="n">
-        <v>0.003968977928161643</v>
+        <v>0.006565773487091087</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -7258,10 +7258,10 @@
         <v>0.89</v>
       </c>
       <c r="D185" t="n">
-        <v>0.8784706592559814</v>
+        <v>0.8906436562538147</v>
       </c>
       <c r="E185" t="n">
-        <v>0.01152934074401857</v>
+        <v>0.0006436562538146839</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -7294,10 +7294,10 @@
         <v>0.85</v>
       </c>
       <c r="D186" t="n">
-        <v>0.8857766389846802</v>
+        <v>0.8975597620010376</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0357766389846802</v>
+        <v>0.04755976200103762</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -7330,10 +7330,10 @@
         <v>0.91</v>
       </c>
       <c r="D187" t="n">
-        <v>0.9053813815116882</v>
+        <v>0.9029572606086731</v>
       </c>
       <c r="E187" t="n">
-        <v>0.004618618488311799</v>
+        <v>0.007042739391326935</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -7366,10 +7366,10 @@
         <v>0.96</v>
       </c>
       <c r="D188" t="n">
-        <v>0.9090341329574585</v>
+        <v>0.9006439447402954</v>
       </c>
       <c r="E188" t="n">
-        <v>0.05096586704254147</v>
+        <v>0.05935605525970455</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -7402,10 +7402,10 @@
         <v>0.67</v>
       </c>
       <c r="D189" t="n">
-        <v>0.6954653263092041</v>
+        <v>0.7040076851844788</v>
       </c>
       <c r="E189" t="n">
-        <v>0.02546532630920406</v>
+        <v>0.03400768518447872</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -7438,10 +7438,10 @@
         <v>0.89</v>
       </c>
       <c r="D190" t="n">
-        <v>0.9388338327407837</v>
+        <v>0.9346997737884521</v>
       </c>
       <c r="E190" t="n">
-        <v>0.04883383274078368</v>
+        <v>0.04469977378845214</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -7474,10 +7474,10 @@
         <v>0.93</v>
       </c>
       <c r="D191" t="n">
-        <v>0.8912620544433594</v>
+        <v>0.8799071311950684</v>
       </c>
       <c r="E191" t="n">
-        <v>0.03873794555664067</v>
+        <v>0.05009286880493169</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -7510,10 +7510,10 @@
         <v>0.86</v>
       </c>
       <c r="D192" t="n">
-        <v>0.9108282327651978</v>
+        <v>0.9089297652244568</v>
       </c>
       <c r="E192" t="n">
-        <v>0.05082823276519777</v>
+        <v>0.0489297652244568</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -7546,10 +7546,10 @@
         <v>0.58</v>
       </c>
       <c r="D193" t="n">
-        <v>0.6468029618263245</v>
+        <v>0.6806197166442871</v>
       </c>
       <c r="E193" t="n">
-        <v>0.0668029618263245</v>
+        <v>0.1006197166442871</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -7582,10 +7582,10 @@
         <v>0.82</v>
       </c>
       <c r="D194" t="n">
-        <v>0.8550456166267395</v>
+        <v>0.8443498611450195</v>
       </c>
       <c r="E194" t="n">
-        <v>0.03504561662673955</v>
+        <v>0.02434986114501958</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -7618,10 +7618,10 @@
         <v>0.87</v>
       </c>
       <c r="D195" t="n">
-        <v>0.8866895437240601</v>
+        <v>0.893816351890564</v>
       </c>
       <c r="E195" t="n">
-        <v>0.01668954372406006</v>
+        <v>0.02381635189056397</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0.93</v>
       </c>
       <c r="D196" t="n">
-        <v>0.9142471551895142</v>
+        <v>0.9058382511138916</v>
       </c>
       <c r="E196" t="n">
-        <v>0.01575284481048589</v>
+        <v>0.02416174888610845</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -7690,10 +7690,10 @@
         <v>0.59</v>
       </c>
       <c r="D197" t="n">
-        <v>0.7069395184516907</v>
+        <v>0.7433292865753174</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1169395184516907</v>
+        <v>0.1533292865753174</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -7726,10 +7726,10 @@
         <v>0.57</v>
       </c>
       <c r="D198" t="n">
-        <v>0.6730998754501343</v>
+        <v>0.6975834369659424</v>
       </c>
       <c r="E198" t="n">
-        <v>0.1030998754501343</v>
+        <v>0.1275834369659424</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -7762,10 +7762,10 @@
         <v>0.2</v>
       </c>
       <c r="D199" t="n">
-        <v>0.3217199146747589</v>
+        <v>0.2843584716320038</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1217199146747589</v>
+        <v>0.08435847163200377</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -7798,10 +7798,10 @@
         <v>0.72</v>
       </c>
       <c r="D200" t="n">
-        <v>0.6530327796936035</v>
+        <v>0.6729506254196167</v>
       </c>
       <c r="E200" t="n">
-        <v>0.06696722030639646</v>
+        <v>0.04704937458038327</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -7834,10 +7834,10 @@
         <v>0.89</v>
       </c>
       <c r="D201" t="n">
-        <v>0.8833385705947876</v>
+        <v>0.8777846097946167</v>
       </c>
       <c r="E201" t="n">
-        <v>0.006661429405212416</v>
+        <v>0.01221539020538331</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -7870,10 +7870,10 @@
         <v>0.84</v>
       </c>
       <c r="D202" t="n">
-        <v>0.8940960168838501</v>
+        <v>0.8901939392089844</v>
       </c>
       <c r="E202" t="n">
-        <v>0.05409601688385013</v>
+        <v>0.05019393920898441</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -7906,10 +7906,10 @@
         <v>0.23</v>
       </c>
       <c r="D203" t="n">
-        <v>0.2728692293167114</v>
+        <v>0.2056623250246048</v>
       </c>
       <c r="E203" t="n">
-        <v>0.04286922931671142</v>
+        <v>0.02433767497539521</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -7942,10 +7942,10 @@
         <v>0.18</v>
       </c>
       <c r="D204" t="n">
-        <v>0.2550432085990906</v>
+        <v>0.2334005534648895</v>
       </c>
       <c r="E204" t="n">
-        <v>0.07504320859909058</v>
+        <v>0.05340055346488953</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -7978,10 +7978,10 @@
         <v>0.58</v>
       </c>
       <c r="D205" t="n">
-        <v>0.6505231857299805</v>
+        <v>0.6585457324981689</v>
       </c>
       <c r="E205" t="n">
-        <v>0.07052318572998051</v>
+        <v>0.07854573249816899</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -8014,10 +8014,10 @@
         <v>0.4</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3059442043304443</v>
+        <v>0.2739143371582031</v>
       </c>
       <c r="E206" t="n">
-        <v>0.09405579566955569</v>
+        <v>0.1260856628417969</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -8050,10 +8050,10 @@
         <v>0.32</v>
       </c>
       <c r="D207" t="n">
-        <v>0.2383317053318024</v>
+        <v>0.2193580716848373</v>
       </c>
       <c r="E207" t="n">
-        <v>0.08166829466819764</v>
+        <v>0.1006419283151627</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -8086,10 +8086,10 @@
         <v>0.41</v>
       </c>
       <c r="D208" t="n">
-        <v>0.356631338596344</v>
+        <v>0.3333815932273865</v>
       </c>
       <c r="E208" t="n">
-        <v>0.05336866140365598</v>
+        <v>0.0766184067726135</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -8122,10 +8122,10 @@
         <v>0.91</v>
       </c>
       <c r="D209" t="n">
-        <v>0.9428914785385132</v>
+        <v>0.9322819709777832</v>
       </c>
       <c r="E209" t="n">
-        <v>0.03289147853851315</v>
+        <v>0.02228197097778317</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -8158,10 +8158,10 @@
         <v>0.28</v>
       </c>
       <c r="D210" t="n">
-        <v>0.2104880511760712</v>
+        <v>0.1967886984348297</v>
       </c>
       <c r="E210" t="n">
-        <v>0.06951194882392886</v>
+        <v>0.08321130156517031</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -8194,10 +8194,10 @@
         <v>0.65</v>
       </c>
       <c r="D211" t="n">
-        <v>0.6393325328826904</v>
+        <v>0.6610469818115234</v>
       </c>
       <c r="E211" t="n">
-        <v>0.01066746711730959</v>
+        <v>0.01104698181152342</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -8230,10 +8230,10 @@
         <v>0.61</v>
       </c>
       <c r="D212" t="n">
-        <v>0.7513884305953979</v>
+        <v>0.7263414263725281</v>
       </c>
       <c r="E212" t="n">
-        <v>0.141388430595398</v>
+        <v>0.1163414263725281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -8266,10 +8266,10 @@
         <v>0.45</v>
       </c>
       <c r="D213" t="n">
-        <v>0.3414034843444824</v>
+        <v>0.3443832397460938</v>
       </c>
       <c r="E213" t="n">
-        <v>0.1085965156555176</v>
+        <v>0.1056167602539063</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -8302,10 +8302,10 @@
         <v>0.91</v>
       </c>
       <c r="D214" t="n">
-        <v>0.945290744304657</v>
+        <v>0.9303085803985596</v>
       </c>
       <c r="E214" t="n">
-        <v>0.03529074430465695</v>
+        <v>0.02030858039855954</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -8338,10 +8338,10 @@
         <v>0.6</v>
       </c>
       <c r="D215" t="n">
-        <v>0.6798285841941833</v>
+        <v>0.7057066559791565</v>
       </c>
       <c r="E215" t="n">
-        <v>0.07982858419418337</v>
+        <v>0.1057066559791565</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -8374,10 +8374,10 @@
         <v>0.77</v>
       </c>
       <c r="D216" t="n">
-        <v>0.7022667527198792</v>
+        <v>0.741705060005188</v>
       </c>
       <c r="E216" t="n">
-        <v>0.06773324728012087</v>
+        <v>0.02829493999481203</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
         <v>0.95</v>
       </c>
       <c r="D217" t="n">
-        <v>0.9274700284004211</v>
+        <v>0.9248318672180176</v>
       </c>
       <c r="E217" t="n">
-        <v>0.02252997159957881</v>
+        <v>0.02516813278198238</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -8446,10 +8446,10 @@
         <v>0.64</v>
       </c>
       <c r="D218" t="n">
-        <v>0.7534299492835999</v>
+        <v>0.723859429359436</v>
       </c>
       <c r="E218" t="n">
-        <v>0.1134299492835998</v>
+        <v>0.08385942935943602</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -8482,10 +8482,10 @@
         <v>0.77</v>
       </c>
       <c r="D219" t="n">
-        <v>0.7401254177093506</v>
+        <v>0.7824723720550537</v>
       </c>
       <c r="E219" t="n">
-        <v>0.02987458229064943</v>
+        <v>0.01247237205505369</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -8518,10 +8518,10 @@
         <v>0.85</v>
       </c>
       <c r="D220" t="n">
-        <v>0.915371835231781</v>
+        <v>0.9173581600189209</v>
       </c>
       <c r="E220" t="n">
-        <v>0.06537183523178103</v>
+        <v>0.06735816001892092</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -8554,10 +8554,10 @@
         <v>0.67</v>
       </c>
       <c r="D221" t="n">
-        <v>0.6693254709243774</v>
+        <v>0.6739911437034607</v>
       </c>
       <c r="E221" t="n">
-        <v>0.0006745290756225986</v>
+        <v>0.003991143703460653</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -8590,10 +8590,10 @@
         <v>0.89</v>
       </c>
       <c r="D222" t="n">
-        <v>0.8836091756820679</v>
+        <v>0.8788868188858032</v>
       </c>
       <c r="E222" t="n">
-        <v>0.006390824317932142</v>
+        <v>0.01111318111419679</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -8626,10 +8626,10 @@
         <v>0.74</v>
       </c>
       <c r="D223" t="n">
-        <v>0.7242518663406372</v>
+        <v>0.7229744791984558</v>
       </c>
       <c r="E223" t="n">
-        <v>0.01574813365936278</v>
+        <v>0.01702552080154418</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -8662,10 +8662,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D224" t="n">
-        <v>0.6861623525619507</v>
+        <v>0.7226124405860901</v>
       </c>
       <c r="E224" t="n">
-        <v>0.003837647438049263</v>
+        <v>0.03261244058609014</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -8698,10 +8698,10 @@
         <v>0.65</v>
       </c>
       <c r="D225" t="n">
-        <v>0.649303674697876</v>
+        <v>0.6614781618118286</v>
       </c>
       <c r="E225" t="n">
-        <v>0.0006963253021240456</v>
+        <v>0.01147816181182859</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         <v>0.95</v>
       </c>
       <c r="D226" t="n">
-        <v>0.9310064911842346</v>
+        <v>0.9248875975608826</v>
       </c>
       <c r="E226" t="n">
-        <v>0.01899350881576534</v>
+        <v>0.02511240243911739</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
         <v>0.66</v>
       </c>
       <c r="D227" t="n">
-        <v>0.684386134147644</v>
+        <v>0.7311548590660095</v>
       </c>
       <c r="E227" t="n">
-        <v>0.02438613414764401</v>
+        <v>0.07115485906600949</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -8806,10 +8806,10 @@
         <v>0.82</v>
       </c>
       <c r="D228" t="n">
-        <v>0.9028661251068115</v>
+        <v>0.896860659122467</v>
       </c>
       <c r="E228" t="n">
-        <v>0.08286612510681157</v>
+        <v>0.07686065912246709</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -8842,10 +8842,10 @@
         <v>0.72</v>
       </c>
       <c r="D229" t="n">
-        <v>0.6893303394317627</v>
+        <v>0.7070128917694092</v>
       </c>
       <c r="E229" t="n">
-        <v>0.03066966056823728</v>
+        <v>0.01298710823059079</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -8878,10 +8878,10 @@
         <v>0.23</v>
       </c>
       <c r="D230" t="n">
-        <v>0.1920865178108215</v>
+        <v>0.1966333091259003</v>
       </c>
       <c r="E230" t="n">
-        <v>0.03791348218917848</v>
+        <v>0.03336669087409974</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -8914,10 +8914,10 @@
         <v>0.86</v>
       </c>
       <c r="D231" t="n">
-        <v>0.8451919555664062</v>
+        <v>0.8358801007270813</v>
       </c>
       <c r="E231" t="n">
-        <v>0.01480804443359374</v>
+        <v>0.02411989927291869</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -8950,10 +8950,10 @@
         <v>0.68</v>
       </c>
       <c r="D232" t="n">
-        <v>0.7356060743331909</v>
+        <v>0.6993018388748169</v>
       </c>
       <c r="E232" t="n">
-        <v>0.05560607433319087</v>
+        <v>0.01930183887481685</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -8986,10 +8986,10 @@
         <v>0.82</v>
       </c>
       <c r="D233" t="n">
-        <v>0.8904637098312378</v>
+        <v>0.8928192853927612</v>
       </c>
       <c r="E233" t="n">
-        <v>0.07046370983123784</v>
+        <v>0.07281928539276128</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -9022,10 +9022,10 @@
         <v>0.89</v>
       </c>
       <c r="D234" t="n">
-        <v>0.9259320497512817</v>
+        <v>0.9289101958274841</v>
       </c>
       <c r="E234" t="n">
-        <v>0.03593204975128172</v>
+        <v>0.03891019582748412</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -9058,10 +9058,10 @@
         <v>0.38</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3543444871902466</v>
+        <v>0.3141126930713654</v>
       </c>
       <c r="E235" t="n">
-        <v>0.02565551280975342</v>
+        <v>0.06588730692863465</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -9094,10 +9094,10 @@
         <v>0.86</v>
       </c>
       <c r="D236" t="n">
-        <v>0.912452220916748</v>
+        <v>0.9019944667816162</v>
       </c>
       <c r="E236" t="n">
-        <v>0.05245222091674806</v>
+        <v>0.04199446678161622</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -9130,10 +9130,10 @@
         <v>0.95</v>
       </c>
       <c r="D237" t="n">
-        <v>0.8893553614616394</v>
+        <v>0.8749574422836304</v>
       </c>
       <c r="E237" t="n">
-        <v>0.06064463853836055</v>
+        <v>0.07504255771636958</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -9166,10 +9166,10 @@
         <v>0.61</v>
       </c>
       <c r="D238" t="n">
-        <v>0.6966384649276733</v>
+        <v>0.6956996917724609</v>
       </c>
       <c r="E238" t="n">
-        <v>0.08663846492767335</v>
+        <v>0.08569969177246095</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -9202,10 +9202,10 @@
         <v>0.25</v>
       </c>
       <c r="D239" t="n">
-        <v>0.2460115551948547</v>
+        <v>0.2296582758426666</v>
       </c>
       <c r="E239" t="n">
-        <v>0.003988444805145264</v>
+        <v>0.02034172415733337</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -9238,10 +9238,10 @@
         <v>0.93</v>
       </c>
       <c r="D240" t="n">
-        <v>0.8732017278671265</v>
+        <v>0.8785362243652344</v>
       </c>
       <c r="E240" t="n">
-        <v>0.05679827213287358</v>
+        <v>0.05146377563476567</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -9274,10 +9274,10 @@
         <v>0.78</v>
       </c>
       <c r="D241" t="n">
-        <v>0.7138034701347351</v>
+        <v>0.7328256368637085</v>
       </c>
       <c r="E241" t="n">
-        <v>0.06619652986526492</v>
+        <v>0.04717436313629153</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -9310,10 +9310,10 @@
         <v>0.92</v>
       </c>
       <c r="D242" t="n">
-        <v>0.886510968208313</v>
+        <v>0.8833179473876953</v>
       </c>
       <c r="E242" t="n">
-        <v>0.03348903179168705</v>
+        <v>0.03668205261230473</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -9346,10 +9346,10 @@
         <v>0.86</v>
       </c>
       <c r="D243" t="n">
-        <v>0.8787931799888611</v>
+        <v>0.8586739897727966</v>
       </c>
       <c r="E243" t="n">
-        <v>0.0187931799888611</v>
+        <v>0.001326010227203356</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -9382,10 +9382,10 @@
         <v>0.61</v>
       </c>
       <c r="D244" t="n">
-        <v>0.6957607269287109</v>
+        <v>0.7324090003967285</v>
       </c>
       <c r="E244" t="n">
-        <v>0.08576072692871095</v>
+        <v>0.1224090003967285</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -9418,10 +9418,10 @@
         <v>0.26</v>
       </c>
       <c r="D245" t="n">
-        <v>0.2785889506340027</v>
+        <v>0.2617547512054443</v>
       </c>
       <c r="E245" t="n">
-        <v>0.01858895063400268</v>
+        <v>0.001754751205444327</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -9454,10 +9454,10 @@
         <v>0.36</v>
       </c>
       <c r="D246" t="n">
-        <v>0.2527139186859131</v>
+        <v>0.1822578012943268</v>
       </c>
       <c r="E246" t="n">
-        <v>0.1072860813140869</v>
+        <v>0.1777421987056732</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -9490,10 +9490,10 @@
         <v>0.6</v>
       </c>
       <c r="D247" t="n">
-        <v>0.6477184295654297</v>
+        <v>0.6710354089736938</v>
       </c>
       <c r="E247" t="n">
-        <v>0.04771842956542971</v>
+        <v>0.07103540897369387</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -9526,10 +9526,10 @@
         <v>0.91</v>
       </c>
       <c r="D248" t="n">
-        <v>0.9414278864860535</v>
+        <v>0.9283031225204468</v>
       </c>
       <c r="E248" t="n">
-        <v>0.03142788648605344</v>
+        <v>0.01830312252044675</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -9562,10 +9562,10 @@
         <v>0.61</v>
       </c>
       <c r="D249" t="n">
-        <v>0.6051225662231445</v>
+        <v>0.6223946809768677</v>
       </c>
       <c r="E249" t="n">
-        <v>0.004877433776855455</v>
+        <v>0.01239468097686769</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -9598,10 +9598,10 @@
         <v>0.71</v>
       </c>
       <c r="D250" t="n">
-        <v>0.6967319250106812</v>
+        <v>0.6857557892799377</v>
       </c>
       <c r="E250" t="n">
-        <v>0.01326807498931881</v>
+        <v>0.02424421072006222</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -9634,10 +9634,10 @@
         <v>0.93</v>
       </c>
       <c r="D251" t="n">
-        <v>0.9466204643249512</v>
+        <v>0.9370390176773071</v>
       </c>
       <c r="E251" t="n">
-        <v>0.01662046432495112</v>
+        <v>0.00703901767730708</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         <v>0.88</v>
       </c>
       <c r="D252" t="n">
-        <v>0.8740278482437134</v>
+        <v>0.8675781488418579</v>
       </c>
       <c r="E252" t="n">
-        <v>0.005972151756286626</v>
+        <v>0.01242185115814209</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         <v>0.65</v>
       </c>
       <c r="D253" t="n">
-        <v>0.6153544783592224</v>
+        <v>0.6425702571868896</v>
       </c>
       <c r="E253" t="n">
-        <v>0.03464552164077761</v>
+        <v>0.007429742813110374</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -9742,10 +9742,10 @@
         <v>0.6</v>
       </c>
       <c r="D254" t="n">
-        <v>0.6777032613754272</v>
+        <v>0.7367659211158752</v>
       </c>
       <c r="E254" t="n">
-        <v>0.07770326137542727</v>
+        <v>0.1367659211158753</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -9778,10 +9778,10 @@
         <v>0.85</v>
       </c>
       <c r="D255" t="n">
-        <v>0.9298101663589478</v>
+        <v>0.9248367547988892</v>
       </c>
       <c r="E255" t="n">
-        <v>0.07981016635894778</v>
+        <v>0.07483675479888918</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -9814,10 +9814,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D256" t="n">
-        <v>0.8428186178207397</v>
+        <v>0.8375964164733887</v>
       </c>
       <c r="E256" t="n">
-        <v>0.0971813821792602</v>
+        <v>0.1024035835266113</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -9850,10 +9850,10 @@
         <v>0.85</v>
       </c>
       <c r="D257" t="n">
-        <v>0.9354569315910339</v>
+        <v>0.9224823713302612</v>
       </c>
       <c r="E257" t="n">
-        <v>0.08545693159103396</v>
+        <v>0.07248237133026125</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -9886,10 +9886,10 @@
         <v>0.91</v>
       </c>
       <c r="D258" t="n">
-        <v>0.9239709973335266</v>
+        <v>0.9066444635391235</v>
       </c>
       <c r="E258" t="n">
-        <v>0.01397099733352658</v>
+        <v>0.003355536460876496</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -9922,10 +9922,10 @@
         <v>0.63</v>
       </c>
       <c r="D259" t="n">
-        <v>0.5479271411895752</v>
+        <v>0.6061992049217224</v>
       </c>
       <c r="E259" t="n">
-        <v>0.08207285881042481</v>
+        <v>0.02380079507827759</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -9958,10 +9958,10 @@
         <v>0.35</v>
       </c>
       <c r="D260" t="n">
-        <v>0.3539113998413086</v>
+        <v>0.3393621444702148</v>
       </c>
       <c r="E260" t="n">
-        <v>0.003911399841308616</v>
+        <v>0.01063785552978513</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -9994,10 +9994,10 @@
         <v>0.34</v>
       </c>
       <c r="D261" t="n">
-        <v>0.2803723216056824</v>
+        <v>0.263112485408783</v>
       </c>
       <c r="E261" t="n">
-        <v>0.05962767839431765</v>
+        <v>0.07688751459121707</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -10030,10 +10030,10 @@
         <v>0.2</v>
       </c>
       <c r="D262" t="n">
-        <v>0.2125033885240555</v>
+        <v>0.1952093243598938</v>
       </c>
       <c r="E262" t="n">
-        <v>0.01250338852405547</v>
+        <v>0.004790675640106212</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -10066,10 +10066,10 @@
         <v>0.62</v>
       </c>
       <c r="D263" t="n">
-        <v>0.6024578809738159</v>
+        <v>0.6316295862197876</v>
       </c>
       <c r="E263" t="n">
-        <v>0.01754211902618408</v>
+        <v>0.0116295862197876</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -10102,10 +10102,10 @@
         <v>0.84</v>
       </c>
       <c r="D264" t="n">
-        <v>0.9081198573112488</v>
+        <v>0.8833671808242798</v>
       </c>
       <c r="E264" t="n">
-        <v>0.06811985731124881</v>
+        <v>0.04336718082427982</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -10138,10 +10138,10 @@
         <v>0.66</v>
       </c>
       <c r="D265" t="n">
-        <v>0.5790764093399048</v>
+        <v>0.6329547762870789</v>
       </c>
       <c r="E265" t="n">
-        <v>0.08092359066009525</v>
+        <v>0.02704522371292117</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -10174,10 +10174,10 @@
         <v>0.87</v>
       </c>
       <c r="D266" t="n">
-        <v>0.9393384456634521</v>
+        <v>0.929151177406311</v>
       </c>
       <c r="E266" t="n">
-        <v>0.06933844566345215</v>
+        <v>0.05915117740631104</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -10210,10 +10210,10 @@
         <v>0.89</v>
       </c>
       <c r="D267" t="n">
-        <v>0.9194110035896301</v>
+        <v>0.9142195582389832</v>
       </c>
       <c r="E267" t="n">
-        <v>0.02941100358963011</v>
+        <v>0.02421955823898314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -10246,10 +10246,10 @@
         <v>0.92</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9248542785644531</v>
+        <v>0.913081169128418</v>
       </c>
       <c r="E268" t="n">
-        <v>0.004854278564453085</v>
+        <v>0.006918830871582071</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="D269" t="n">
-        <v>0.7570602893829346</v>
+        <v>0.7708871364593506</v>
       </c>
       <c r="E269" t="n">
-        <v>0.1970602893829345</v>
+        <v>0.2108871364593505</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -10318,10 +10318,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D270" t="n">
-        <v>0.928584098815918</v>
+        <v>0.9138214588165283</v>
       </c>
       <c r="E270" t="n">
-        <v>0.01141590118408198</v>
+        <v>0.02617854118347163</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -10354,10 +10354,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D271" t="n">
-        <v>0.6783706545829773</v>
+        <v>0.675470232963562</v>
       </c>
       <c r="E271" t="n">
-        <v>0.01162934541702265</v>
+        <v>0.01452976703643793</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -10390,10 +10390,10 @@
         <v>0.32</v>
       </c>
       <c r="D272" t="n">
-        <v>0.3621446192264557</v>
+        <v>0.3248549103736877</v>
       </c>
       <c r="E272" t="n">
-        <v>0.04214461922645568</v>
+        <v>0.004854910373687737</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -10426,10 +10426,10 @@
         <v>0.95</v>
       </c>
       <c r="D273" t="n">
-        <v>0.9414277076721191</v>
+        <v>0.9340453743934631</v>
       </c>
       <c r="E273" t="n">
-        <v>0.008572292327880815</v>
+        <v>0.01595462560653682</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -10462,10 +10462,10 @@
         <v>0.92</v>
       </c>
       <c r="D274" t="n">
-        <v>0.9225112199783325</v>
+        <v>0.9117929339408875</v>
       </c>
       <c r="E274" t="n">
-        <v>0.00251121997833248</v>
+        <v>0.008207066059112589</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -10498,10 +10498,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D275" t="n">
-        <v>0.9149787425994873</v>
+        <v>0.9190160632133484</v>
       </c>
       <c r="E275" t="n">
-        <v>0.02502125740051264</v>
+        <v>0.02098393678665156</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -10534,10 +10534,10 @@
         <v>0.32</v>
       </c>
       <c r="D276" t="n">
-        <v>0.2594152092933655</v>
+        <v>0.2349925637245178</v>
       </c>
       <c r="E276" t="n">
-        <v>0.06058479070663453</v>
+        <v>0.08500743627548218</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -10570,10 +10570,10 @@
         <v>0.25</v>
       </c>
       <c r="D277" t="n">
-        <v>0.2311845123767853</v>
+        <v>0.2323652505874634</v>
       </c>
       <c r="E277" t="n">
-        <v>0.01881548762321472</v>
+        <v>0.01763474941253662</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -10606,10 +10606,10 @@
         <v>0.57</v>
       </c>
       <c r="D278" t="n">
-        <v>0.5994675755500793</v>
+        <v>0.6471230387687683</v>
       </c>
       <c r="E278" t="n">
-        <v>0.02946757555007939</v>
+        <v>0.07712303876876836</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -10642,10 +10642,10 @@
         <v>0.82</v>
       </c>
       <c r="D279" t="n">
-        <v>0.8557513952255249</v>
+        <v>0.8478972911834717</v>
       </c>
       <c r="E279" t="n">
-        <v>0.03575139522552495</v>
+        <v>0.02789729118347173</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -10678,10 +10678,10 @@
         <v>0.6</v>
       </c>
       <c r="D280" t="n">
-        <v>0.7430955767631531</v>
+        <v>0.7904155850410461</v>
       </c>
       <c r="E280" t="n">
-        <v>0.1430955767631531</v>
+        <v>0.1904155850410462</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -10714,10 +10714,10 @@
         <v>0.76</v>
       </c>
       <c r="D281" t="n">
-        <v>0.7140322923660278</v>
+        <v>0.7249030470848083</v>
       </c>
       <c r="E281" t="n">
-        <v>0.04596770763397218</v>
+        <v>0.03509695291519166</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -10750,10 +10750,10 @@
         <v>0.65</v>
       </c>
       <c r="D282" t="n">
-        <v>0.7704460620880127</v>
+        <v>0.7358813881874084</v>
       </c>
       <c r="E282" t="n">
-        <v>0.1204460620880127</v>
+        <v>0.08588138818740843</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -10786,10 +10786,10 @@
         <v>0.71</v>
       </c>
       <c r="D283" t="n">
-        <v>0.7231558561325073</v>
+        <v>0.7345488667488098</v>
       </c>
       <c r="E283" t="n">
-        <v>0.01315585613250736</v>
+        <v>0.02454886674880985</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -10822,10 +10822,10 @@
         <v>0.26</v>
       </c>
       <c r="D284" t="n">
-        <v>0.2933588922023773</v>
+        <v>0.2866165041923523</v>
       </c>
       <c r="E284" t="n">
-        <v>0.03335889220237731</v>
+        <v>0.02661650419235229</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -10858,10 +10858,10 @@
         <v>0.74</v>
       </c>
       <c r="D285" t="n">
-        <v>0.6627139449119568</v>
+        <v>0.7006357908248901</v>
       </c>
       <c r="E285" t="n">
-        <v>0.0772860550880432</v>
+        <v>0.03936420917510985</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>0.43</v>
       </c>
       <c r="D286" t="n">
-        <v>0.319655179977417</v>
+        <v>0.3096740245819092</v>
       </c>
       <c r="E286" t="n">
-        <v>0.110344820022583</v>
+        <v>0.1203259754180908</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -10930,10 +10930,10 @@
         <v>0.85</v>
       </c>
       <c r="D287" t="n">
-        <v>0.8575724363327026</v>
+        <v>0.8437736034393311</v>
       </c>
       <c r="E287" t="n">
-        <v>0.007572436332702659</v>
+        <v>0.006226396560668923</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -10966,10 +10966,10 @@
         <v>0.83</v>
       </c>
       <c r="D288" t="n">
-        <v>0.887702465057373</v>
+        <v>0.8745639324188232</v>
       </c>
       <c r="E288" t="n">
-        <v>0.05770246505737309</v>
+        <v>0.04456393241882328</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -11002,10 +11002,10 @@
         <v>0.66</v>
       </c>
       <c r="D289" t="n">
-        <v>0.7038558721542358</v>
+        <v>0.7232025265693665</v>
       </c>
       <c r="E289" t="n">
-        <v>0.04385587215423581</v>
+        <v>0.06320252656936642</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -11038,10 +11038,10 @@
         <v>0.83</v>
       </c>
       <c r="D290" t="n">
-        <v>0.8886482715606689</v>
+        <v>0.8876979351043701</v>
       </c>
       <c r="E290" t="n">
-        <v>0.05864827156066899</v>
+        <v>0.05769793510437016</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -11074,10 +11074,10 @@
         <v>0.92</v>
       </c>
       <c r="D291" t="n">
-        <v>0.9001439213752747</v>
+        <v>0.8953342437744141</v>
       </c>
       <c r="E291" t="n">
-        <v>0.01985607862472538</v>
+        <v>0.02466575622558598</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -11110,10 +11110,10 @@
         <v>0.83</v>
       </c>
       <c r="D292" t="n">
-        <v>0.9062391519546509</v>
+        <v>0.9005484580993652</v>
       </c>
       <c r="E292" t="n">
-        <v>0.07623915195465092</v>
+        <v>0.07054845809936527</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -11146,10 +11146,10 @@
         <v>0.72</v>
       </c>
       <c r="D293" t="n">
-        <v>0.5861575603485107</v>
+        <v>0.6386028528213501</v>
       </c>
       <c r="E293" t="n">
-        <v>0.1338424396514892</v>
+        <v>0.08139714717864988</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -11182,10 +11182,10 @@
         <v>0.92</v>
       </c>
       <c r="D294" t="n">
-        <v>0.9327833652496338</v>
+        <v>0.9200071096420288</v>
       </c>
       <c r="E294" t="n">
-        <v>0.01278336524963375</v>
+        <v>7.109642028768626e-06</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -11218,10 +11218,10 @@
         <v>0.92</v>
       </c>
       <c r="D295" t="n">
-        <v>0.8857806921005249</v>
+        <v>0.8594677448272705</v>
       </c>
       <c r="E295" t="n">
-        <v>0.03421930789947514</v>
+        <v>0.06053225517272953</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -11254,10 +11254,10 @@
         <v>0.89</v>
       </c>
       <c r="D296" t="n">
-        <v>0.9085800647735596</v>
+        <v>0.8959858417510986</v>
       </c>
       <c r="E296" t="n">
-        <v>0.01858006477355956</v>
+        <v>0.005985841751098619</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -11290,10 +11290,10 @@
         <v>0.74</v>
       </c>
       <c r="D297" t="n">
-        <v>0.6678964495658875</v>
+        <v>0.6961072683334351</v>
       </c>
       <c r="E297" t="n">
-        <v>0.07210355043411254</v>
+        <v>0.04389273166656493</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -11326,10 +11326,10 @@
         <v>0.64</v>
       </c>
       <c r="D298" t="n">
-        <v>0.6367653012275696</v>
+        <v>0.6673352122306824</v>
       </c>
       <c r="E298" t="n">
-        <v>0.003234698772430433</v>
+        <v>0.02733521223068236</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -11362,10 +11362,10 @@
         <v>0.95</v>
       </c>
       <c r="D299" t="n">
-        <v>0.9334115386009216</v>
+        <v>0.9185871481895447</v>
       </c>
       <c r="E299" t="n">
-        <v>0.01658846139907832</v>
+        <v>0.03141285181045528</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -11398,10 +11398,10 @@
         <v>0.43</v>
       </c>
       <c r="D300" t="n">
-        <v>0.3359814286231995</v>
+        <v>0.3186484575271606</v>
       </c>
       <c r="E300" t="n">
-        <v>0.09401857137680053</v>
+        <v>0.1113515424728393</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -11434,10 +11434,10 @@
         <v>0.9</v>
       </c>
       <c r="D301" t="n">
-        <v>0.9207140207290649</v>
+        <v>0.9058608412742615</v>
       </c>
       <c r="E301" t="n">
-        <v>0.02071402072906492</v>
+        <v>0.005860841274261452</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>

--- a/reports/model_comparison_report.xlsx
+++ b/reports/model_comparison_report.xlsx
@@ -507,13 +507,13 @@
         <v>0.5355</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5594</v>
+        <v>1.7938</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8024</v>
+        <v>3.9487</v>
       </c>
       <c r="K2" t="n">
-        <v>0.018683</v>
+        <v>0.026325</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -547,16 +547,16 @@
         <v>0.6994</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0741</v>
+        <v>0.0989</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8496</v>
+        <v>3.768</v>
       </c>
       <c r="K3" t="n">
-        <v>0.018997</v>
+        <v>0.02512</v>
       </c>
       <c r="L3" t="n">
-        <v>87.58</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="4">
@@ -587,16 +587,16 @@
         <v>0.5355</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3172</v>
+        <v>0.3279</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7033</v>
+        <v>4.9201</v>
       </c>
       <c r="K4" t="n">
-        <v>0.024689</v>
+        <v>0.032801</v>
       </c>
       <c r="L4" t="n">
-        <v>5.74</v>
+        <v>5.86</v>
       </c>
     </row>
   </sheetData>
